--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513498.1335012931</v>
+        <v>513498</v>
       </c>
       <c r="R2" t="n">
-        <v>6358110.474711431</v>
+        <v>6358110</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1042,12 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513498.1335012931</v>
+        <v>513498</v>
       </c>
       <c r="R5" t="n">
-        <v>6358110.474711431</v>
+        <v>6358110</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1112,19 +1092,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1288,12 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513497.2641095038</v>
+        <v>513497</v>
       </c>
       <c r="R7" t="n">
-        <v>6358210.239569597</v>
+        <v>6358210</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1358,19 +1323,9 @@
           <t>1993-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1414,12 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513498.1335012931</v>
+        <v>513498</v>
       </c>
       <c r="R8" t="n">
-        <v>6358110.474711431</v>
+        <v>6358110</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1484,19 +1434,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1540,12 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513497.2641095038</v>
+        <v>513497</v>
       </c>
       <c r="R9" t="n">
-        <v>6358210.239569597</v>
+        <v>6358210</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1610,19 +1545,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104223</v>
+        <v>104232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104232</v>
+        <v>104235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104235</v>
+        <v>104262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104262</v>
+        <v>104268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104268</v>
+        <v>104275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104275</v>
+        <v>104279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104279</v>
+        <v>104286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104289</v>
+        <v>104294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104294</v>
+        <v>104302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968345</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>74154187</v>
       </c>
       <c r="B5" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>74222782</v>
       </c>
       <c r="B7" t="n">
-        <v>104302</v>
+        <v>104312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>74553215</v>
       </c>
       <c r="B8" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>74552538</v>
       </c>
       <c r="B9" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39152-2022 artfynd.xlsx
+++ b/artfynd/A 39152-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885686</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74553215</t>
         </is>
       </c>
     </row>
@@ -991,6 +1006,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885726</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119051</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74222782</t>
         </is>
       </c>
     </row>
@@ -1318,6 +1348,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885670</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552538</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74154187</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1690,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73885676</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,8 +1806,25 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73968345</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>